--- a/InputData/elec/CDRDfRCP/Cln Dsptchble Rsrc Dmnd for Rlbty Curve Param.xlsx
+++ b/InputData/elec/CDRDfRCP/Cln Dsptchble Rsrc Dmnd for Rlbty Curve Param.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\CDRDfRCP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\VT\elec\CDRDfRCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5650AD1B-C0BA-4B3D-AD2B-DEFFB05BA2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE8F3057-6ECC-44A9-9EE2-12C545692235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DDCF7A3C-4581-48BB-A680-D5CBB461C8EB}"/>
+    <workbookView xWindow="2310" yWindow="1035" windowWidth="11385" windowHeight="15660" xr2:uid="{DDCF7A3C-4581-48BB-A680-D5CBB461C8EB}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>CDRDfRCP Clean Dispatchable Resource Demand for Reliabilty Curve Paramaters</t>
   </si>
@@ -70,6 +70,15 @@
   </si>
   <si>
     <t>Required clena firm</t>
+  </si>
+  <si>
+    <t>We avoid having this increase too sharply in the last few percent of requirement to avoid</t>
+  </si>
+  <si>
+    <t>artificially high CES credit prices in the model.</t>
+  </si>
+  <si>
+    <t>Vermont</t>
   </si>
 </sst>
 </file>
@@ -403,151 +412,151 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="49"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1.3345183610335988E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.7757968180565077E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.3503723246920407E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.0948404411468292E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4.0548669420009678E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>5.2871968066592338E-5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>6.8620531956736788E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>8.8659893966219769E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.551115123125783E-18</c:v>
+                  <c:v>1.1405263483894035E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.6653345369377351E-17</c:v>
+                  <c:v>1.4609811682472217E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.1062266354383615E-17</c:v>
+                  <c:v>1.8637901468158136E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.0539125955565397E-16</c:v>
+                  <c:v>2.3681548265671039E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.6058269965196816E-16</c:v>
+                  <c:v>2.9972778773873499E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.1149748619109233E-15</c:v>
+                  <c:v>3.7790817418671967E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.6502359175046883E-15</c:v>
+                  <c:v>4.7470257398569141E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.0539125955565396E-14</c:v>
+                  <c:v>5.9410250432745957E-4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6.2400085099056931E-14</c:v>
+                  <c:v>7.4084704568779251E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.8650636590678006E-13</c:v>
+                  <c:v>9.2053410628561982E-4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.4873883215122991E-13</c:v>
+                  <c:v>1.1397391661842615E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.5899781491413023E-12</c:v>
+                  <c:v>1.406138252443695E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.5389081382296588E-12</c:v>
+                  <c:v>1.7286299009540041E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.2771117496868101E-11</c:v>
+                  <c:v>2.1174481702520621E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3.5431807487995574E-11</c:v>
+                  <c:v>2.5842552420247689E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>9.6963675977335131E-11</c:v>
+                  <c:v>3.1421976435896727E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.6183864521023282E-10</c:v>
+                  <c:v>3.8059045878387158E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.9794099943898406E-10</c:v>
+                  <c:v>4.5914003965626393E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.8370015453239576E-9</c:v>
+                  <c:v>5.5158957263671321E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.7758002441611331E-9</c:v>
+                  <c:v>6.5974149898884119E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.2267704280199966E-8</c:v>
+                  <c:v>7.8542111497937779E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3.1145162993073687E-8</c:v>
+                  <c:v>9.3039159295859718E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.8172304796009229E-8</c:v>
+                  <c:v>1.0962376409663188E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.9403068323153861E-7</c:v>
+                  <c:v>1.2842142086152065E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4.7638569630192865E-7</c:v>
+                  <c:v>1.4950594952808677E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.15725410513301E-6</c:v>
+                  <c:v>1.7287764710475297E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2.7821855297760492E-6</c:v>
+                  <c:v>1.9843946630412508E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>6.6210903952146356E-6</c:v>
+                  <c:v>2.2597342306981179E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.5600803848198064E-5</c:v>
+                  <c:v>2.5512067623070053E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>3.6400444973472278E-5</c:v>
+                  <c:v>2.853699948673204E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>8.4107941297706379E-5</c:v>
+                  <c:v>3.1606027941427882E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.9243394277213E-4</c:v>
+                  <c:v>3.4640289033344603E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>4.3571467423015323E-4</c:v>
+                  <c:v>3.7552809826340114E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>9.7491479588711078E-4</c:v>
+                  <c:v>4.0255641018243658E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2.1483338811260355E-3</c:v>
+                  <c:v>4.2668969178507668E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>4.6277060486618286E-3</c:v>
+                  <c:v>4.4730964824285228E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>9.5923357822252763E-3</c:v>
+                  <c:v>4.640643664684916E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.8541891846878166E-2</c:v>
+                  <c:v>4.7692043118172142E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>3.1606027941427882E-2</c:v>
+                  <c:v>4.8616190328389854E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>4.4125085859779797E-2</c:v>
+                  <c:v>4.9232966777728315E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>4.9471822020543572E-2</c:v>
+                  <c:v>4.9611286513068079E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1651,7 +1660,12 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2">
+        <v>45723</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1679,6 +1693,16 @@
         <v>6</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
@@ -1693,7 +1717,7 @@
       </c>
       <c r="B15" s="4">
         <f>(1-EXP(-((A15)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>0</v>
+        <v>1.3345183610335988E-5</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1702,7 +1726,7 @@
       </c>
       <c r="B16" s="4">
         <f>(1-EXP(-((A16)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>0</v>
+        <v>1.7757968180565077E-5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1711,7 +1735,7 @@
       </c>
       <c r="B17" s="4">
         <f>(1-EXP(-((A17)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>0</v>
+        <v>2.3503723246920407E-5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1720,7 +1744,7 @@
       </c>
       <c r="B18" s="4">
         <f>(1-EXP(-((A18)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>0</v>
+        <v>3.0948404411468292E-5</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1729,7 +1753,7 @@
       </c>
       <c r="B19" s="4">
         <f>(1-EXP(-((A19)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>0</v>
+        <v>4.0548669420009678E-5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1738,7 +1762,7 @@
       </c>
       <c r="B20" s="4">
         <f>(1-EXP(-((A20)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>0</v>
+        <v>5.2871968066592338E-5</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1747,7 +1771,7 @@
       </c>
       <c r="B21" s="4">
         <f>(1-EXP(-((A21)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>0</v>
+        <v>6.8620531956736788E-5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1756,7 +1780,7 @@
       </c>
       <c r="B22" s="4">
         <f>(1-EXP(-((A22)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>0</v>
+        <v>8.8659893966219769E-5</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1765,7 +1789,7 @@
       </c>
       <c r="B23" s="4">
         <f>(1-EXP(-((A23)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>5.551115123125783E-18</v>
+        <v>1.1405263483894035E-4</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1774,7 +1798,7 @@
       </c>
       <c r="B24" s="4">
         <f>(1-EXP(-((A24)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.6653345369377351E-17</v>
+        <v>1.4609811682472217E-4</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1783,7 +1807,7 @@
       </c>
       <c r="B25" s="4">
         <f>(1-EXP(-((A25)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>6.1062266354383615E-17</v>
+        <v>1.8637901468158136E-4</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1792,7 +1816,7 @@
       </c>
       <c r="B26" s="4">
         <f>(1-EXP(-((A26)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>2.0539125955565397E-16</v>
+        <v>2.3681548265671039E-4</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1801,7 +1825,7 @@
       </c>
       <c r="B27" s="4">
         <f>(1-EXP(-((A27)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>6.6058269965196816E-16</v>
+        <v>2.9972778773873499E-4</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1810,7 +1834,7 @@
       </c>
       <c r="B28" s="4">
         <f>(1-EXP(-((A28)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>2.1149748619109233E-15</v>
+        <v>3.7790817418671967E-4</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1819,7 +1843,7 @@
       </c>
       <c r="B29" s="4">
         <f>(1-EXP(-((A29)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>6.6502359175046883E-15</v>
+        <v>4.7470257398569141E-4</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1828,7 +1852,7 @@
       </c>
       <c r="B30" s="4">
         <f>(1-EXP(-((A30)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>2.0539125955565396E-14</v>
+        <v>5.9410250432745957E-4</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1837,7 +1861,7 @@
       </c>
       <c r="B31" s="4">
         <f>(1-EXP(-((A31)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>6.2400085099056931E-14</v>
+        <v>7.4084704568779251E-4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1846,7 +1870,7 @@
       </c>
       <c r="B32" s="4">
         <f>(1-EXP(-((A32)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.8650636590678006E-13</v>
+        <v>9.2053410628561982E-4</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1855,7 +1879,7 @@
       </c>
       <c r="B33" s="4">
         <f>(1-EXP(-((A33)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>5.4873883215122991E-13</v>
+        <v>1.1397391661842615E-3</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1864,7 +1888,7 @@
       </c>
       <c r="B34" s="4">
         <f>(1-EXP(-((A34)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.5899781491413023E-12</v>
+        <v>1.406138252443695E-3</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1873,7 +1897,7 @@
       </c>
       <c r="B35" s="4">
         <f>(1-EXP(-((A35)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>4.5389081382296588E-12</v>
+        <v>1.7286299009540041E-3</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1882,7 +1906,7 @@
       </c>
       <c r="B36" s="4">
         <f>(1-EXP(-((A36)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.2771117496868101E-11</v>
+        <v>2.1174481702520621E-3</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1891,7 +1915,7 @@
       </c>
       <c r="B37" s="4">
         <f>(1-EXP(-((A37)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>3.5431807487995574E-11</v>
+        <v>2.5842552420247689E-3</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1900,7 +1924,7 @@
       </c>
       <c r="B38" s="4">
         <f>(1-EXP(-((A38)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>9.6963675977335131E-11</v>
+        <v>3.1421976435896727E-3</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1909,7 +1933,7 @@
       </c>
       <c r="B39" s="4">
         <f>(1-EXP(-((A39)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>2.6183864521023282E-10</v>
+        <v>3.8059045878387158E-3</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1918,7 +1942,7 @@
       </c>
       <c r="B40" s="4">
         <f>(1-EXP(-((A40)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>6.9794099943898406E-10</v>
+        <v>4.5914003965626393E-3</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1927,7 +1951,7 @@
       </c>
       <c r="B41" s="4">
         <f>(1-EXP(-((A41)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.8370015453239576E-9</v>
+        <v>5.5158957263671321E-3</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1936,7 +1960,7 @@
       </c>
       <c r="B42" s="4">
         <f>(1-EXP(-((A42)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>4.7758002441611331E-9</v>
+        <v>6.5974149898884119E-3</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1945,7 +1969,7 @@
       </c>
       <c r="B43" s="4">
         <f>(1-EXP(-((A43)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.2267704280199966E-8</v>
+        <v>7.8542111497937779E-3</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1954,7 +1978,7 @@
       </c>
       <c r="B44" s="4">
         <f>(1-EXP(-((A44)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>3.1145162993073687E-8</v>
+        <v>9.3039159295859718E-3</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1963,7 +1987,7 @@
       </c>
       <c r="B45" s="4">
         <f>(1-EXP(-((A45)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>7.8172304796009229E-8</v>
+        <v>1.0962376409663188E-2</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1972,7 +1996,7 @@
       </c>
       <c r="B46" s="4">
         <f>(1-EXP(-((A46)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.9403068323153861E-7</v>
+        <v>1.2842142086152065E-2</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1981,7 +2005,7 @@
       </c>
       <c r="B47" s="4">
         <f>(1-EXP(-((A47)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>4.7638569630192865E-7</v>
+        <v>1.4950594952808677E-2</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1990,7 +2014,7 @@
       </c>
       <c r="B48" s="4">
         <f>(1-EXP(-((A48)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.15725410513301E-6</v>
+        <v>1.7287764710475297E-2</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1999,7 +2023,7 @@
       </c>
       <c r="B49" s="4">
         <f>(1-EXP(-((A49)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>2.7821855297760492E-6</v>
+        <v>1.9843946630412508E-2</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2008,7 +2032,7 @@
       </c>
       <c r="B50" s="4">
         <f>(1-EXP(-((A50)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>6.6210903952146356E-6</v>
+        <v>2.2597342306981179E-2</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2017,7 +2041,7 @@
       </c>
       <c r="B51" s="4">
         <f>(1-EXP(-((A51)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.5600803848198064E-5</v>
+        <v>2.5512067623070053E-2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2026,7 +2050,7 @@
       </c>
       <c r="B52" s="4">
         <f>(1-EXP(-((A52)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>3.6400444973472278E-5</v>
+        <v>2.853699948673204E-2</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2035,7 +2059,7 @@
       </c>
       <c r="B53" s="4">
         <f>(1-EXP(-((A53)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>8.4107941297706379E-5</v>
+        <v>3.1606027941427882E-2</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2044,7 +2068,7 @@
       </c>
       <c r="B54" s="4">
         <f>(1-EXP(-((A54)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.9243394277213E-4</v>
+        <v>3.4640289033344603E-2</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2053,7 +2077,7 @@
       </c>
       <c r="B55" s="4">
         <f>(1-EXP(-((A55)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>4.3571467423015323E-4</v>
+        <v>3.7552809826340114E-2</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2062,7 +2086,7 @@
       </c>
       <c r="B56" s="4">
         <f>(1-EXP(-((A56)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>9.7491479588711078E-4</v>
+        <v>4.0255641018243658E-2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2071,7 +2095,7 @@
       </c>
       <c r="B57" s="4">
         <f>(1-EXP(-((A57)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>2.1483338811260355E-3</v>
+        <v>4.2668969178507668E-2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2080,7 +2104,7 @@
       </c>
       <c r="B58" s="4">
         <f>(1-EXP(-((A58)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>4.6277060486618286E-3</v>
+        <v>4.4730964824285228E-2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2089,7 +2113,7 @@
       </c>
       <c r="B59" s="4">
         <f>(1-EXP(-((A59)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>9.5923357822252763E-3</v>
+        <v>4.640643664684916E-2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2098,7 +2122,7 @@
       </c>
       <c r="B60" s="4">
         <f>(1-EXP(-((A60)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>1.8541891846878166E-2</v>
+        <v>4.7692043118172142E-2</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2107,7 +2131,7 @@
       </c>
       <c r="B61" s="4">
         <f>(1-EXP(-((A61)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>3.1606027941427882E-2</v>
+        <v>4.8616190328389854E-2</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2116,7 +2140,7 @@
       </c>
       <c r="B62" s="4">
         <f>(1-EXP(-((A62)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>4.4125085859779797E-2</v>
+        <v>4.9232966777728315E-2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2125,7 +2149,7 @@
       </c>
       <c r="B63" s="4">
         <f>(1-EXP(-((A63)/CDRDfRCP!$B$2)^CDRDfRCP!$B$1))*CDRDfRCP!$B$3</f>
-        <v>4.9471822020543572E-2</v>
+        <v>4.9611286513068079E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2150,7 +2174,7 @@
         <v>7</v>
       </c>
       <c r="B1">
-        <v>75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2158,7 +2182,7 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
